--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="139">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -76,6 +79,75 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1917 бул. Асен Йорданов</t>
+  </si>
+  <si>
+    <t>1112 София Резбарска</t>
+  </si>
+  <si>
+    <t>1185 София Дружба 1</t>
+  </si>
+  <si>
+    <t>1161 София Шипченски проход</t>
+  </si>
+  <si>
+    <t>1127 Благоевград</t>
+  </si>
+  <si>
+    <t>1916 О5 Ахелой</t>
+  </si>
+  <si>
+    <t>1905 София, О5 Люлин</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1910 О5 Бургас</t>
+  </si>
+  <si>
     <t>СВ4779СТ</t>
   </si>
   <si>
@@ -94,15 +166,30 @@
     <t>СА9195ММ</t>
   </si>
   <si>
+    <t>СВ7119КК</t>
+  </si>
+  <si>
     <t>СВ2261ХН</t>
   </si>
   <si>
-    <t>СВ7119КК</t>
-  </si>
-  <si>
     <t>СВ1088ЕО</t>
   </si>
   <si>
+    <t>СВ0420ХМ</t>
+  </si>
+  <si>
+    <t>СВ0422ХМ</t>
+  </si>
+  <si>
+    <t>СВ0901ОА</t>
+  </si>
+  <si>
+    <t>СВ5362ТН</t>
+  </si>
+  <si>
+    <t>СВ2114НН</t>
+  </si>
+  <si>
     <t>78970156027720558</t>
   </si>
   <si>
@@ -121,49 +208,211 @@
     <t>78970156027720517</t>
   </si>
   <si>
+    <t>78970156027720566</t>
+  </si>
+  <si>
     <t>78970156027720608</t>
   </si>
   <si>
-    <t>78970156027720566</t>
-  </si>
-  <si>
     <t>78970156027720632</t>
   </si>
   <si>
+    <t>78970156027720616</t>
+  </si>
+  <si>
+    <t>78970156027720624</t>
+  </si>
+  <si>
+    <t>78970156027720640</t>
+  </si>
+  <si>
+    <t>78970156027720590</t>
+  </si>
+  <si>
+    <t>78970156027720541</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>11:24</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>14:09</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>16:03</t>
-  </si>
-  <si>
-    <t>12:11</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>11:41</t>
-  </si>
-  <si>
-    <t>09:26</t>
-  </si>
-  <si>
-    <t>08:52</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:23:00</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>14:10:00</t>
+  </si>
+  <si>
+    <t>12:26:00</t>
+  </si>
+  <si>
+    <t>16:03:00</t>
+  </si>
+  <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
+    <t>12:12:00</t>
+  </si>
+  <si>
+    <t>11:41:00</t>
+  </si>
+  <si>
+    <t>09:26:00</t>
+  </si>
+  <si>
+    <t>08:52:00</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>11:55:00</t>
+  </si>
+  <si>
+    <t>16:17:00</t>
+  </si>
+  <si>
+    <t>06:55:00</t>
+  </si>
+  <si>
+    <t>11:05:00</t>
+  </si>
+  <si>
+    <t>13:10:00</t>
+  </si>
+  <si>
+    <t>14:44:00</t>
+  </si>
+  <si>
+    <t>13:27:00</t>
+  </si>
+  <si>
+    <t>10:11:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>10:36:00</t>
+  </si>
+  <si>
+    <t>14:56:00</t>
+  </si>
+  <si>
+    <t>07:43:00</t>
+  </si>
+  <si>
+    <t>06:51:00</t>
+  </si>
+  <si>
+    <t>13:34:00</t>
+  </si>
+  <si>
+    <t>13:11:00</t>
+  </si>
+  <si>
+    <t>14:53:00</t>
+  </si>
+  <si>
+    <t>3231415618 3231415618</t>
+  </si>
+  <si>
+    <t>3231454747 3231454747</t>
+  </si>
+  <si>
+    <t>3231735587 3231735587</t>
+  </si>
+  <si>
+    <t>3231774913 3231774913</t>
+  </si>
+  <si>
+    <t>3231775258 3231775258</t>
+  </si>
+  <si>
+    <t>3231762705 3231762705</t>
+  </si>
+  <si>
+    <t>3231820965 3231820965</t>
+  </si>
+  <si>
+    <t>3231822234 3231822234</t>
+  </si>
+  <si>
+    <t>3231885978 3231885978</t>
+  </si>
+  <si>
+    <t>3231872726 3231872726</t>
+  </si>
+  <si>
+    <t>3231920000 3231920000</t>
+  </si>
+  <si>
+    <t>3232050318 3232050318</t>
+  </si>
+  <si>
+    <t>3232032517 3232032517</t>
+  </si>
+  <si>
+    <t>3232099515 3232099515</t>
+  </si>
+  <si>
+    <t>3232075963 3232075963</t>
+  </si>
+  <si>
+    <t>3232155632 3232155632</t>
+  </si>
+  <si>
+    <t>3232139040 3232139040</t>
+  </si>
+  <si>
+    <t>3232153334 3232153334</t>
+  </si>
+  <si>
+    <t>3232144041 3232144041</t>
+  </si>
+  <si>
+    <t>3232123508 3232123508</t>
+  </si>
+  <si>
+    <t>3232199159 3232199159</t>
+  </si>
+  <si>
+    <t>3232167073 3232167073</t>
+  </si>
+  <si>
+    <t>3232250615 3232250615</t>
+  </si>
+  <si>
+    <t>3232432002 3232432002</t>
+  </si>
+  <si>
+    <t>3232400476 3232400476</t>
+  </si>
+  <si>
+    <t>3232438159 3232438159</t>
+  </si>
+  <si>
+    <t>3232466281 3232466281</t>
+  </si>
+  <si>
+    <t>3232470200 3232470200</t>
+  </si>
+  <si>
+    <t>3232484097 3232484097</t>
+  </si>
+  <si>
+    <t>3232575114 3232575114</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС АД % ГРУПА 1</t>
@@ -587,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -596,16 +845,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -645,529 +895,1421 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1172</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F2">
         <v>68.18000000000001</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>113.18</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>122.72</v>
       </c>
-      <c r="K2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>75</v>
       </c>
       <c r="M2">
-        <v>154315</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1184</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F3">
         <v>83.72</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>138.98</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>150.7</v>
       </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>76</v>
       </c>
       <c r="M3">
-        <v>493346</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1198</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F4">
         <v>33.15</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4">
         <v>1.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>54.7</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.81</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>60</v>
       </c>
-      <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>77</v>
       </c>
       <c r="M4">
-        <v>329210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1120</v>
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F5">
         <v>217.75</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5">
         <v>1.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>359.29</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.81</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>394.13</v>
       </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>78</v>
       </c>
       <c r="M5">
-        <v>74639</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1152</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F6">
         <v>34.39</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6">
         <v>1.65</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>56.74</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.79</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>61.56</v>
       </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>79</v>
       </c>
       <c r="M6">
-        <v>194780</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>1917</v>
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>212.71</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7">
         <v>1.65</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>350.97</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.79</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>380.75</v>
       </c>
-      <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>80</v>
       </c>
       <c r="M7">
-        <v>448144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>1184</v>
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8">
+        <v>1.65</v>
+      </c>
+      <c r="I8" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="J8">
+        <v>1.78</v>
+      </c>
+      <c r="K8" s="1">
+        <v>89</v>
+      </c>
+      <c r="L8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9">
+        <v>48.5</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9">
+        <v>1.65</v>
+      </c>
+      <c r="I9" s="1">
+        <v>80.02</v>
+      </c>
+      <c r="J9">
+        <v>1.78</v>
+      </c>
+      <c r="K9" s="1">
+        <v>86.33</v>
+      </c>
+      <c r="L9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8">
-        <v>48.5</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="H8">
-        <v>80.02</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="J8">
-        <v>86.33</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>498486</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9">
-        <v>1184</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="H9">
-        <v>82.5</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="J9">
-        <v>89</v>
-      </c>
-      <c r="K9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>498591</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10">
-        <v>1112</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F10">
         <v>81.12</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10">
         <v>1.65</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>133.85</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.77</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>143.58</v>
       </c>
-      <c r="K10" t="s">
-        <v>47</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>83</v>
       </c>
       <c r="M10">
-        <v>231953</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11">
-        <v>1185</v>
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F11">
         <v>50.61</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11">
         <v>1.65</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>83.51000000000001</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.77</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>89.58</v>
       </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>84</v>
       </c>
       <c r="M11">
-        <v>145903</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>10710</v>
+      </c>
+      <c r="N11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12">
-        <v>1184</v>
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F12">
         <v>34.09</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12">
         <v>1.64</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>55.91</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.76</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>60</v>
       </c>
-      <c r="K12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+      <c r="L12" t="s">
+        <v>85</v>
       </c>
       <c r="M12">
-        <v>87082</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13">
+        <v>52.88</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13">
+        <v>1.64</v>
+      </c>
+      <c r="I13" s="1">
+        <v>86.72</v>
+      </c>
+      <c r="J13">
+        <v>1.75</v>
+      </c>
+      <c r="K13" s="1">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>62.39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14">
+        <v>1.64</v>
+      </c>
+      <c r="I14" s="1">
+        <v>102.32</v>
+      </c>
+      <c r="J14">
+        <v>1.74</v>
+      </c>
+      <c r="K14" s="1">
+        <v>108.56</v>
+      </c>
+      <c r="L14" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15">
+        <v>82.19</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15">
+        <v>1.63</v>
+      </c>
+      <c r="I15" s="1">
+        <v>133.97</v>
+      </c>
+      <c r="J15">
+        <v>1.75</v>
+      </c>
+      <c r="K15" s="1">
+        <v>143.83</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16">
+        <v>69.95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16">
+        <v>1.63</v>
+      </c>
+      <c r="I16" s="1">
+        <v>114.02</v>
+      </c>
+      <c r="J16">
+        <v>1.75</v>
+      </c>
+      <c r="K16" s="1">
+        <v>122.41</v>
+      </c>
+      <c r="L16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17">
+        <v>67.66</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17">
+        <v>1.63</v>
+      </c>
+      <c r="I17" s="1">
+        <v>110.29</v>
+      </c>
+      <c r="J17">
+        <v>1.74</v>
+      </c>
+      <c r="K17" s="1">
+        <v>117.73</v>
+      </c>
+      <c r="L17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18">
+        <v>29.4</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18">
+        <v>1.63</v>
+      </c>
+      <c r="I18" s="1">
+        <v>47.92</v>
+      </c>
+      <c r="J18">
+        <v>1.75</v>
+      </c>
+      <c r="K18" s="1">
+        <v>51.45</v>
+      </c>
+      <c r="L18" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19">
+        <v>35.29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19">
+        <v>1.87</v>
+      </c>
+      <c r="I19" s="1">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>70.58</v>
+      </c>
+      <c r="L19" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20">
+        <v>57.07</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20">
+        <v>1.63</v>
+      </c>
+      <c r="I20" s="1">
+        <v>93.02</v>
+      </c>
+      <c r="J20">
+        <v>1.75</v>
+      </c>
+      <c r="K20" s="1">
+        <v>99.87</v>
+      </c>
+      <c r="L20" t="s">
+        <v>92</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21">
+        <v>79.78</v>
+      </c>
+      <c r="G21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21">
+        <v>1.63</v>
+      </c>
+      <c r="I21" s="1">
+        <v>130.04</v>
+      </c>
+      <c r="J21">
+        <v>1.74</v>
+      </c>
+      <c r="K21" s="1">
+        <v>138.82</v>
+      </c>
+      <c r="L21" t="s">
+        <v>93</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22">
+        <v>1.63</v>
+      </c>
+      <c r="I22" s="1">
+        <v>40.75</v>
+      </c>
+      <c r="J22">
+        <v>1.75</v>
+      </c>
+      <c r="K22" s="1">
+        <v>43.75</v>
+      </c>
+      <c r="L22" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23">
+        <v>54.59</v>
+      </c>
+      <c r="G23" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23">
+        <v>1.63</v>
+      </c>
+      <c r="I23" s="1">
+        <v>88.98</v>
+      </c>
+      <c r="J23">
+        <v>1.74</v>
+      </c>
+      <c r="K23" s="1">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L23" t="s">
+        <v>95</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="D24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24">
+        <v>19.38</v>
+      </c>
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24">
+        <v>1.63</v>
+      </c>
+      <c r="I24" s="1">
+        <v>31.59</v>
+      </c>
+      <c r="J24">
+        <v>1.74</v>
+      </c>
+      <c r="K24" s="1">
+        <v>33.72</v>
+      </c>
+      <c r="L24" t="s">
+        <v>96</v>
+      </c>
+      <c r="M24">
+        <v>11024</v>
+      </c>
+      <c r="N24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25">
+        <v>54.26</v>
+      </c>
+      <c r="G25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25">
+        <v>1.63</v>
+      </c>
+      <c r="I25" s="1">
+        <v>88.44</v>
+      </c>
+      <c r="J25">
+        <v>1.72</v>
+      </c>
+      <c r="K25" s="1">
+        <v>93.33</v>
+      </c>
+      <c r="L25" t="s">
+        <v>97</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26">
+        <v>55.09</v>
+      </c>
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26">
+        <v>1.63</v>
+      </c>
+      <c r="I26" s="1">
+        <v>89.8</v>
+      </c>
+      <c r="J26">
+        <v>1.72</v>
+      </c>
+      <c r="K26" s="1">
+        <v>94.75</v>
+      </c>
+      <c r="L26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27">
+        <v>40</v>
+      </c>
+      <c r="G27" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27">
+        <v>1.63</v>
+      </c>
+      <c r="I27" s="1">
+        <v>65.2</v>
+      </c>
+      <c r="J27">
+        <v>1.75</v>
+      </c>
+      <c r="K27" s="1">
+        <v>70</v>
+      </c>
+      <c r="L27" t="s">
+        <v>99</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="G28" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28">
+        <v>1.63</v>
+      </c>
+      <c r="I28" s="1">
+        <v>104.84</v>
+      </c>
+      <c r="J28">
+        <v>1.72</v>
+      </c>
+      <c r="K28" s="1">
+        <v>110.63</v>
+      </c>
+      <c r="L28" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29">
+        <v>69.06</v>
+      </c>
+      <c r="G29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H29">
+        <v>1.63</v>
+      </c>
+      <c r="I29" s="1">
+        <v>112.57</v>
+      </c>
+      <c r="J29">
+        <v>1.74</v>
+      </c>
+      <c r="K29" s="1">
+        <v>120.16</v>
+      </c>
+      <c r="L29" t="s">
+        <v>101</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="6">
-        <v>914.22</v>
-      </c>
-      <c r="C17" s="6">
-        <v>11</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.6513</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1509.65</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1638.35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="9">
-        <v>914.22</v>
-      </c>
-      <c r="C18" s="9">
-        <v>11</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9">
-        <v>1509.65</v>
-      </c>
-      <c r="F18" s="9">
-        <v>1638.35</v>
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30">
+        <v>68</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30">
+        <v>1.63</v>
+      </c>
+      <c r="I30" s="1">
+        <v>110.84</v>
+      </c>
+      <c r="J30">
+        <v>1.72</v>
+      </c>
+      <c r="K30" s="1">
+        <v>116.96</v>
+      </c>
+      <c r="L30" t="s">
+        <v>102</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31">
+        <v>35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H31">
+        <v>1.87</v>
+      </c>
+      <c r="I31" s="1">
+        <v>65.45</v>
+      </c>
+      <c r="J31">
+        <v>1.96</v>
+      </c>
+      <c r="K31" s="1">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="L31" t="s">
+        <v>101</v>
+      </c>
+      <c r="M31">
+        <v>11562</v>
+      </c>
+      <c r="N31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="6">
+        <v>1865.24</v>
+      </c>
+      <c r="C36" s="6">
+        <v>28</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1.6411</v>
+      </c>
+      <c r="E36" s="6">
+        <v>3060.96</v>
+      </c>
+      <c r="F36" s="6">
+        <v>3291.85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="6">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="C37" s="6">
+        <v>2</v>
+      </c>
+      <c r="D37" s="7">
+        <v>1.87</v>
+      </c>
+      <c r="E37" s="6">
+        <v>131.44</v>
+      </c>
+      <c r="F37" s="6">
+        <v>139.18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" s="9">
+        <v>1935.53</v>
+      </c>
+      <c r="C38" s="9">
+        <v>30</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="9">
+        <v>3192.4</v>
+      </c>
+      <c r="F38" s="9">
+        <v>3431.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A34:F34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
@@ -466,7 +466,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,12 +476,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,17 +525,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="132">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -70,31 +76,76 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>АМ Тракия</t>
-  </si>
-  <si>
-    <t>София Дружба 2</t>
-  </si>
-  <si>
-    <t>Пловдив Пещерско шосе</t>
-  </si>
-  <si>
-    <t>Пазарджик</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>София Асен Йорданов</t>
-  </si>
-  <si>
-    <t>София Чепинци</t>
-  </si>
-  <si>
-    <t>Тракия Езеро</t>
-  </si>
-  <si>
-    <t>Радиново</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1142 Пазарджик Север</t>
+  </si>
+  <si>
+    <t>1150 Пловдив, Пещерско шосе</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1917 бул. Асен Йорданов</t>
+  </si>
+  <si>
+    <t>1183 София Чепинци</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1905 София, О5 Люлин</t>
+  </si>
+  <si>
+    <t>1908 О5 Стара Загора</t>
+  </si>
+  <si>
+    <t>1139 София Ломско шосе</t>
   </si>
   <si>
     <t>СВ0420ХМ</t>
@@ -103,97 +154,244 @@
     <t>СВ1283СТ</t>
   </si>
   <si>
+    <t>СВ7594АЕ</t>
+  </si>
+  <si>
+    <t>СВ0422ХМ</t>
+  </si>
+  <si>
     <t>СВ2261ХН</t>
   </si>
   <si>
-    <t>СВ0422ХМ</t>
-  </si>
-  <si>
-    <t>СВ7594АЕ</t>
+    <t>СВ7119КК</t>
   </si>
   <si>
     <t>СВ4779СТ</t>
   </si>
   <si>
-    <t>СВ7119КК</t>
-  </si>
-  <si>
     <t>СВ4064ХА</t>
   </si>
   <si>
     <t>СВ0901ОА</t>
   </si>
   <si>
+    <t>СВ5362ТН</t>
+  </si>
+  <si>
+    <t>СА7292АВ</t>
+  </si>
+  <si>
+    <t>СВ3481ХА</t>
+  </si>
+  <si>
+    <t>СА9195ММ</t>
+  </si>
+  <si>
+    <t>СВ2114НН</t>
+  </si>
+  <si>
     <t>78970156027720616</t>
   </si>
   <si>
     <t>78970156027720533</t>
   </si>
   <si>
+    <t>78970156027720657</t>
+  </si>
+  <si>
+    <t>78970156027720624</t>
+  </si>
+  <si>
     <t>78970156027720608</t>
   </si>
   <si>
-    <t>78970156027720624</t>
-  </si>
-  <si>
-    <t>78970156027720657</t>
+    <t>78970156027720566</t>
   </si>
   <si>
     <t>78970156027720558</t>
   </si>
   <si>
-    <t>78970156027720566</t>
-  </si>
-  <si>
     <t>78970156027720525</t>
   </si>
   <si>
     <t>78970156027720640</t>
   </si>
   <si>
+    <t>78970156027720590</t>
+  </si>
+  <si>
+    <t>78970156027720509</t>
+  </si>
+  <si>
+    <t>78970156027720582</t>
+  </si>
+  <si>
+    <t>78970156027720517</t>
+  </si>
+  <si>
+    <t>78970156027720541</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>10 Л. ДOБABKA ADPLUS ДИЗEЛOBИ ДBИГATEЛИ</t>
-  </si>
-  <si>
-    <t>2026-07-02 12:37:02</t>
-  </si>
-  <si>
-    <t>2026-07-06 14:25:04</t>
-  </si>
-  <si>
-    <t>2026-07-08 06:55:33</t>
-  </si>
-  <si>
-    <t>2026-07-08 13:21:03</t>
-  </si>
-  <si>
-    <t>2026-07-08 14:25:57</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:08:35</t>
-  </si>
-  <si>
-    <t>2026-07-13 11:38:16</t>
-  </si>
-  <si>
-    <t>2026-07-13 11:38:17</t>
-  </si>
-  <si>
-    <t>2026-07-13 15:42:25</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:31:00</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:58:21</t>
-  </si>
-  <si>
-    <t>2026-07-15 10:27:01</t>
+    <t>10L ADPLUS DIESEL ADDITIVE</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>12:36:00</t>
+  </si>
+  <si>
+    <t>14:25:00</t>
+  </si>
+  <si>
+    <t>13:20:00</t>
+  </si>
+  <si>
+    <t>06:55:00</t>
+  </si>
+  <si>
+    <t>09:08:00</t>
+  </si>
+  <si>
+    <t>15:42:00</t>
+  </si>
+  <si>
+    <t>11:38:00</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>09:56:00</t>
+  </si>
+  <si>
+    <t>10:27:00</t>
+  </si>
+  <si>
+    <t>11:34:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>11:21:00</t>
+  </si>
+  <si>
+    <t>06:34:00</t>
+  </si>
+  <si>
+    <t>09:34:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>12:09:00</t>
+  </si>
+  <si>
+    <t>09:49:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>12:47:00</t>
+  </si>
+  <si>
+    <t>10:32:00</t>
+  </si>
+  <si>
+    <t>11:54:00</t>
+  </si>
+  <si>
+    <t>06:51:00</t>
+  </si>
+  <si>
+    <t>3234202532 3234202532</t>
+  </si>
+  <si>
+    <t>3234396571 3234396571</t>
+  </si>
+  <si>
+    <t>3234462576 3234462576</t>
+  </si>
+  <si>
+    <t>3234475487 3234475487</t>
+  </si>
+  <si>
+    <t>3234465520 3234465520</t>
+  </si>
+  <si>
+    <t>3234734283 3234734283</t>
+  </si>
+  <si>
+    <t>3234738761 3234738761</t>
+  </si>
+  <si>
+    <t>3234721404 3234721404</t>
+  </si>
+  <si>
+    <t>3234786317 3234786317</t>
+  </si>
+  <si>
+    <t>3234766148 3234766148</t>
+  </si>
+  <si>
+    <t>3234832385 3234832385</t>
+  </si>
+  <si>
+    <t>3234885600 3234885600</t>
+  </si>
+  <si>
+    <t>3234890656 3234890656</t>
+  </si>
+  <si>
+    <t>3234926150 3234926150</t>
+  </si>
+  <si>
+    <t>3235088633 3235088633</t>
+  </si>
+  <si>
+    <t>3235142057 3235142057</t>
+  </si>
+  <si>
+    <t>3235196340 3235196340</t>
+  </si>
+  <si>
+    <t>3235147266 3235147266</t>
+  </si>
+  <si>
+    <t>3235213748 3235213748</t>
+  </si>
+  <si>
+    <t>3235239508 3235239508</t>
+  </si>
+  <si>
+    <t>3235274605 3235274605</t>
+  </si>
+  <si>
+    <t>3235443000 3235443000</t>
+  </si>
+  <si>
+    <t>3235464227 3235464227</t>
+  </si>
+  <si>
+    <t>3235541321 3235541321</t>
+  </si>
+  <si>
+    <t>3235526785 3235526785</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС АД % ГРУПА 1</t>
@@ -611,7 +809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -620,15 +818,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -665,574 +865,1268 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F2">
         <v>75.48</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>107.94</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.55</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>116.99</v>
       </c>
-      <c r="K2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F3">
         <v>81.43000000000001</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>117.26</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>123.77</v>
       </c>
-      <c r="K3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F4">
-        <v>40.02</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.68</v>
+        <v>40.78</v>
+      </c>
+      <c r="G4" t="s">
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>67.23</v>
+        <v>1.44</v>
       </c>
       <c r="I4" s="1">
-        <v>1.78</v>
+        <v>58.72</v>
       </c>
       <c r="J4">
-        <v>71.23999999999999</v>
-      </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1.52</v>
+      </c>
+      <c r="K4" s="1">
+        <v>61.99</v>
+      </c>
+      <c r="L4" t="s">
+        <v>78</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F5">
         <v>73.05</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5">
         <v>1.44</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>105.19</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>110.31</v>
       </c>
-      <c r="K5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6">
+        <v>40.02</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>1.68</v>
+      </c>
+      <c r="I6" s="1">
+        <v>67.23</v>
+      </c>
+      <c r="J6">
+        <v>1.78</v>
+      </c>
+      <c r="K6" s="1">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
         <v>45</v>
       </c>
-      <c r="F6">
-        <v>40.78</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H6">
-        <v>58.72</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J6">
-        <v>61.99</v>
-      </c>
-      <c r="K6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>80.83</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7">
         <v>1.48</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>119.63</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.58</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>127.71</v>
       </c>
-      <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F8">
+        <v>45.16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8">
+        <v>1.48</v>
+      </c>
+      <c r="I8" s="1">
+        <v>66.84</v>
+      </c>
+      <c r="J8">
+        <v>1.56</v>
+      </c>
+      <c r="K8" s="1">
+        <v>70.45</v>
+      </c>
+      <c r="L8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9">
         <v>80.84</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9">
         <v>1.48</v>
       </c>
-      <c r="H8">
+      <c r="I9" s="1">
         <v>119.64</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J9">
         <v>1.55</v>
       </c>
-      <c r="J8">
+      <c r="K9" s="1">
         <v>125.3</v>
       </c>
-      <c r="K8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9">
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10">
         <v>26.83</v>
       </c>
-      <c r="H9">
+      <c r="I10" s="1">
         <v>26.83</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J10">
         <v>26.83</v>
       </c>
-      <c r="J9">
+      <c r="K10" s="1">
         <v>26.83</v>
       </c>
-      <c r="K9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10">
-        <v>45.16</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H10">
-        <v>66.84</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J10">
-        <v>70.45</v>
-      </c>
-      <c r="K10" t="s">
-        <v>56</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="L10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F11">
         <v>335</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11">
         <v>1.5</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>502.5</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.57</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>525.95</v>
       </c>
-      <c r="K11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="L11" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F12">
         <v>56.94</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12">
         <v>1.5</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>85.41</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.59</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>90.53</v>
       </c>
-      <c r="K12" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="L12" t="s">
+        <v>85</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F13">
         <v>82.66</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13">
         <v>1.52</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>125.64</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.61</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>133.08</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>51.01</v>
+      </c>
+      <c r="G14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14">
+        <v>1.53</v>
+      </c>
+      <c r="I14" s="1">
+        <v>78.05</v>
+      </c>
+      <c r="J14">
+        <v>1.64</v>
+      </c>
+      <c r="K14" s="1">
+        <v>83.66</v>
+      </c>
+      <c r="L14" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15">
+        <v>56.38</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15">
+        <v>1.53</v>
+      </c>
+      <c r="I15" s="1">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="J15">
+        <v>1.62</v>
+      </c>
+      <c r="K15" s="1">
+        <v>91.34</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16">
+        <v>120.23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16">
+        <v>1.53</v>
+      </c>
+      <c r="I16" s="1">
+        <v>183.95</v>
+      </c>
+      <c r="J16">
+        <v>1.62</v>
+      </c>
+      <c r="K16" s="1">
+        <v>194.77</v>
+      </c>
+      <c r="L16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17">
+        <v>31.7</v>
+      </c>
+      <c r="G17" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17">
+        <v>1.71</v>
+      </c>
+      <c r="I17" s="1">
+        <v>54.21</v>
+      </c>
+      <c r="J17">
+        <v>1.94</v>
+      </c>
+      <c r="K17" s="1">
+        <v>61.5</v>
+      </c>
+      <c r="L17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18">
+        <v>56.23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18">
+        <v>1.59</v>
+      </c>
+      <c r="I18" s="1">
+        <v>89.41</v>
+      </c>
+      <c r="J18">
+        <v>1.71</v>
+      </c>
+      <c r="K18" s="1">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19">
+        <v>73.23</v>
+      </c>
+      <c r="G19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19">
+        <v>1.62</v>
+      </c>
+      <c r="I19" s="1">
+        <v>118.63</v>
+      </c>
+      <c r="J19">
+        <v>1.7</v>
+      </c>
+      <c r="K19" s="1">
+        <v>124.49</v>
+      </c>
+      <c r="L19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20">
+        <v>63.18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20">
+        <v>1.62</v>
+      </c>
+      <c r="I20" s="1">
+        <v>102.35</v>
+      </c>
+      <c r="J20">
+        <v>1.69</v>
+      </c>
+      <c r="K20" s="1">
+        <v>106.77</v>
+      </c>
+      <c r="L20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
         <v>59</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21">
+        <v>74.75</v>
+      </c>
+      <c r="G21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21">
+        <v>1.62</v>
+      </c>
+      <c r="I21" s="1">
+        <v>121.1</v>
+      </c>
+      <c r="J21">
+        <v>1.71</v>
+      </c>
+      <c r="K21" s="1">
+        <v>127.82</v>
+      </c>
+      <c r="L21" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="E22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22">
+        <v>50.06</v>
+      </c>
+      <c r="G22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22">
+        <v>1.73</v>
+      </c>
+      <c r="I22" s="1">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="J22">
+        <v>1.96</v>
+      </c>
+      <c r="K22" s="1">
+        <v>98.12</v>
+      </c>
+      <c r="L22" t="s">
+        <v>95</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23">
+        <v>177.56</v>
+      </c>
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23">
+        <v>1.65</v>
+      </c>
+      <c r="I23" s="1">
+        <v>292.97</v>
+      </c>
+      <c r="J23">
+        <v>1.71</v>
+      </c>
+      <c r="K23" s="1">
+        <v>303.63</v>
+      </c>
+      <c r="L23" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24">
+        <v>54.53</v>
+      </c>
+      <c r="G24" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24">
+        <v>1.65</v>
+      </c>
+      <c r="I24" s="1">
+        <v>89.97</v>
+      </c>
+      <c r="J24">
+        <v>1.76</v>
+      </c>
+      <c r="K24" s="1">
+        <v>95.97</v>
+      </c>
+      <c r="L24" t="s">
+        <v>97</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="G25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25">
+        <v>1.68</v>
+      </c>
+      <c r="I25" s="1">
+        <v>122.62</v>
+      </c>
+      <c r="J25">
+        <v>1.74</v>
+      </c>
+      <c r="K25" s="1">
+        <v>127</v>
+      </c>
+      <c r="L25" t="s">
+        <v>98</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6">
-        <v>952.17</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26">
+        <v>81.67</v>
+      </c>
+      <c r="G26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26">
+        <v>1.7</v>
+      </c>
+      <c r="I26" s="1">
+        <v>138.84</v>
+      </c>
+      <c r="J26">
+        <v>1.74</v>
+      </c>
+      <c r="K26" s="1">
+        <v>142.11</v>
+      </c>
+      <c r="L26" t="s">
+        <v>99</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27">
+        <v>39.76</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27">
+        <v>1.8</v>
+      </c>
+      <c r="I27" s="1">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>79.52</v>
+      </c>
+      <c r="L27" t="s">
+        <v>100</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="7">
-        <v>1.4795</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1408.77</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1486.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="6">
-        <v>40.02</v>
-      </c>
-      <c r="C19" s="6">
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="6">
+        <v>1833.93</v>
+      </c>
+      <c r="C32" s="6">
+        <v>21</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1.5447</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2832.92</v>
+      </c>
+      <c r="F32" s="6">
+        <v>2979.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="6">
+        <v>161.54</v>
+      </c>
+      <c r="C33" s="6">
+        <v>4</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1.7309</v>
+      </c>
+      <c r="E33" s="6">
+        <v>279.61</v>
+      </c>
+      <c r="F33" s="6">
+        <v>310.38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="6">
         <v>1</v>
       </c>
-      <c r="D19" s="7">
-        <v>1.6799</v>
-      </c>
-      <c r="E19" s="6">
-        <v>67.23</v>
-      </c>
-      <c r="F19" s="6">
-        <v>71.23999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="6">
+      <c r="C34" s="6">
         <v>1</v>
       </c>
-      <c r="C20" s="6">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="D34" s="7">
         <v>26.83</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E34" s="6">
         <v>26.83</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F34" s="6">
         <v>26.83</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="9">
-        <v>993.1900000000001</v>
-      </c>
-      <c r="C21" s="9">
-        <v>12</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9">
-        <v>1502.83</v>
-      </c>
-      <c r="F21" s="9">
-        <v>1584.15</v>
+    <row r="35" spans="1:6">
+      <c r="A35" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="9">
+        <v>1996.47</v>
+      </c>
+      <c r="C35" s="9">
+        <v>26</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="9">
+        <v>3139.36</v>
+      </c>
+      <c r="F35" s="9">
+        <v>3317</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
@@ -418,7 +418,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -2057,7 +2057,7 @@
         <v>21</v>
       </c>
       <c r="D32" s="7">
-        <v>1.5447</v>
+        <v>1.544726</v>
       </c>
       <c r="E32" s="6">
         <v>2832.92</v>
@@ -2077,7 +2077,7 @@
         <v>4</v>
       </c>
       <c r="D33" s="7">
-        <v>1.7309</v>
+        <v>1.730903</v>
       </c>
       <c r="E33" s="6">
         <v>279.61</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 1/ДЕМАКС АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="132">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -420,8 +417,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -514,10 +511,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,7 +809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -825,13 +822,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -874,407 +871,380 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F2">
         <v>75.477</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I2" s="1">
-        <v>1.429</v>
+        <v>107.857</v>
       </c>
       <c r="J2">
-        <v>107.856633</v>
+        <v>1.55</v>
       </c>
       <c r="K2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L2" s="1">
-        <v>116.98935</v>
-      </c>
-      <c r="M2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>116.989</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3">
         <v>81.428</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I3" s="1">
-        <v>1.436</v>
+        <v>116.931</v>
       </c>
       <c r="J3">
-        <v>116.930608</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
-        <v>123.77056</v>
-      </c>
-      <c r="M3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>123.771</v>
+      </c>
+      <c r="L3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4">
         <v>40.783</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I4" s="1">
-        <v>1.442</v>
+        <v>58.809</v>
       </c>
       <c r="J4">
-        <v>58.809086</v>
+        <v>1.52</v>
       </c>
       <c r="K4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L4" s="1">
-        <v>61.99016</v>
-      </c>
-      <c r="M4" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>61.99</v>
+      </c>
+      <c r="L4" t="s">
+        <v>78</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5">
         <v>73.04600000000001</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I5" s="1">
-        <v>1.442</v>
+        <v>105.332</v>
       </c>
       <c r="J5">
-        <v>105.332332</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>110.29946</v>
-      </c>
-      <c r="M5" t="s">
-        <v>80</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>110.299</v>
+      </c>
+      <c r="L5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6">
         <v>40.022</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I6" s="1">
-        <v>1.679</v>
+        <v>67.197</v>
       </c>
       <c r="J6">
-        <v>67.196938</v>
+        <v>1.78</v>
       </c>
       <c r="K6" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L6" s="1">
-        <v>71.23916</v>
-      </c>
-      <c r="M6" t="s">
-        <v>81</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>71.239</v>
+      </c>
+      <c r="L6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>80.82899999999999</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I7" s="1">
-        <v>1.481</v>
+        <v>119.708</v>
       </c>
       <c r="J7">
-        <v>119.707749</v>
+        <v>1.58</v>
       </c>
       <c r="K7" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L7" s="1">
-        <v>127.70982</v>
-      </c>
-      <c r="M7" t="s">
-        <v>82</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>127.71</v>
+      </c>
+      <c r="L7" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8">
         <v>45.16</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I8" s="1">
-        <v>1.481</v>
+        <v>66.88200000000001</v>
       </c>
       <c r="J8">
-        <v>66.88196000000001</v>
+        <v>1.56</v>
       </c>
       <c r="K8" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L8" s="1">
-        <v>70.4496</v>
-      </c>
-      <c r="M8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>70.45</v>
+      </c>
+      <c r="L8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>80.839</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I9" s="1">
-        <v>1.481</v>
+        <v>119.723</v>
       </c>
       <c r="J9">
-        <v>119.722559</v>
+        <v>1.55</v>
       </c>
       <c r="K9" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L9" s="1">
-        <v>125.30045</v>
-      </c>
-      <c r="M9" t="s">
-        <v>84</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>125.3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10">
         <v>26.83</v>
@@ -1288,821 +1258,767 @@
       <c r="K10" s="1">
         <v>26.83</v>
       </c>
-      <c r="L10" s="1">
-        <v>26.83</v>
-      </c>
-      <c r="M10" t="s">
-        <v>84</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11">
         <v>335</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11">
-        <v>1.469</v>
+        <v>1.499</v>
       </c>
       <c r="I11" s="1">
-        <v>1.499</v>
+        <v>502.165</v>
       </c>
       <c r="J11">
-        <v>502.165</v>
+        <v>1.57</v>
       </c>
       <c r="K11" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="L11" s="1">
         <v>525.95</v>
       </c>
-      <c r="M11" t="s">
-        <v>85</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12">
         <v>56.937</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H12">
-        <v>1.469</v>
+        <v>1.499</v>
       </c>
       <c r="I12" s="1">
-        <v>1.499</v>
+        <v>85.349</v>
       </c>
       <c r="J12">
-        <v>85.348563</v>
+        <v>1.59</v>
       </c>
       <c r="K12" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="L12" s="1">
-        <v>90.52983</v>
-      </c>
-      <c r="M12" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>90.53</v>
+      </c>
+      <c r="L12" t="s">
+        <v>85</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13">
         <v>82.658</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13">
-        <v>1.489</v>
+        <v>1.519</v>
       </c>
       <c r="I13" s="1">
-        <v>1.519</v>
+        <v>125.558</v>
       </c>
       <c r="J13">
-        <v>125.557502</v>
+        <v>1.61</v>
       </c>
       <c r="K13" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L13" s="1">
-        <v>133.07938</v>
-      </c>
-      <c r="M13" t="s">
-        <v>87</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>133.079</v>
+      </c>
+      <c r="L13" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14">
         <v>51.012</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H14">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I14" s="1">
-        <v>1.529</v>
+        <v>77.997</v>
       </c>
       <c r="J14">
-        <v>77.997348</v>
+        <v>1.64</v>
       </c>
       <c r="K14" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="L14" s="1">
-        <v>83.65967999999999</v>
-      </c>
-      <c r="M14" t="s">
-        <v>88</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>83.66</v>
+      </c>
+      <c r="L14" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15">
         <v>56.383</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I15" s="1">
-        <v>1.529</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J15">
-        <v>86.20960700000001</v>
+        <v>1.62</v>
       </c>
       <c r="K15" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="L15" s="1">
-        <v>91.34045999999999</v>
-      </c>
-      <c r="M15" t="s">
-        <v>89</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>91.34</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16">
         <v>120.228</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I16" s="1">
-        <v>1.529</v>
+        <v>183.829</v>
       </c>
       <c r="J16">
-        <v>183.828612</v>
+        <v>1.62</v>
       </c>
       <c r="K16" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="L16" s="1">
-        <v>194.76936</v>
-      </c>
-      <c r="M16" t="s">
-        <v>90</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>194.769</v>
+      </c>
+      <c r="L16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17">
         <v>31.701</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H17">
-        <v>1.628</v>
+        <v>1.708</v>
       </c>
       <c r="I17" s="1">
-        <v>1.708</v>
+        <v>54.145</v>
       </c>
       <c r="J17">
-        <v>54.145308</v>
+        <v>1.94</v>
       </c>
       <c r="K17" s="1">
-        <v>1.94</v>
-      </c>
-      <c r="L17" s="1">
-        <v>61.49994</v>
-      </c>
-      <c r="M17" t="s">
-        <v>91</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>61.5</v>
+      </c>
+      <c r="L17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18">
         <v>56.228</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H18">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I18" s="1">
-        <v>1.594</v>
+        <v>89.627</v>
       </c>
       <c r="J18">
-        <v>89.627432</v>
+        <v>1.71</v>
       </c>
       <c r="K18" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L18" s="1">
-        <v>96.14988</v>
-      </c>
-      <c r="M18" t="s">
-        <v>92</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19">
         <v>73.229</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I19" s="1">
-        <v>1.618</v>
+        <v>118.485</v>
       </c>
       <c r="J19">
-        <v>118.484522</v>
+        <v>1.7</v>
       </c>
       <c r="K19" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="1">
-        <v>124.4893</v>
-      </c>
-      <c r="M19" t="s">
-        <v>93</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>124.489</v>
+      </c>
+      <c r="L19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20">
         <v>63.178</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I20" s="1">
-        <v>1.618</v>
+        <v>102.222</v>
       </c>
       <c r="J20">
-        <v>102.222004</v>
+        <v>1.69</v>
       </c>
       <c r="K20" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L20" s="1">
-        <v>106.77082</v>
-      </c>
-      <c r="M20" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>106.771</v>
+      </c>
+      <c r="L20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21">
         <v>74.749</v>
       </c>
       <c r="G21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H21">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I21" s="1">
-        <v>1.618</v>
+        <v>120.944</v>
       </c>
       <c r="J21">
-        <v>120.943882</v>
+        <v>1.71</v>
       </c>
       <c r="K21" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L21" s="1">
-        <v>127.82079</v>
-      </c>
-      <c r="M21" t="s">
-        <v>95</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>127.821</v>
+      </c>
+      <c r="L21" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22">
         <v>50.061</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I22" s="1">
-        <v>1.728</v>
+        <v>86.505</v>
       </c>
       <c r="J22">
-        <v>86.505408</v>
+        <v>1.96</v>
       </c>
       <c r="K22" s="1">
-        <v>1.96</v>
-      </c>
-      <c r="L22" s="1">
-        <v>98.11956000000001</v>
-      </c>
-      <c r="M22" t="s">
-        <v>96</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>98.12</v>
+      </c>
+      <c r="L22" t="s">
+        <v>95</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23">
         <v>177.561</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H23">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I23" s="1">
-        <v>1.649</v>
+        <v>292.798</v>
       </c>
       <c r="J23">
-        <v>292.798089</v>
+        <v>1.71</v>
       </c>
       <c r="K23" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L23" s="1">
-        <v>303.62931</v>
-      </c>
-      <c r="M23" t="s">
-        <v>97</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>303.629</v>
+      </c>
+      <c r="L23" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
         <v>72</v>
-      </c>
-      <c r="E24" t="s">
-        <v>73</v>
       </c>
       <c r="F24">
         <v>54.528</v>
       </c>
       <c r="G24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I24" s="1">
-        <v>1.649</v>
+        <v>89.917</v>
       </c>
       <c r="J24">
-        <v>89.91667200000001</v>
+        <v>1.76</v>
       </c>
       <c r="K24" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L24" s="1">
-        <v>95.96928</v>
-      </c>
-      <c r="M24" t="s">
-        <v>98</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>95.96899999999999</v>
+      </c>
+      <c r="L24" t="s">
+        <v>97</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F25">
         <v>72.989</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I25" s="1">
-        <v>1.683</v>
+        <v>122.84</v>
       </c>
       <c r="J25">
-        <v>122.840487</v>
+        <v>1.74</v>
       </c>
       <c r="K25" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L25" s="1">
-        <v>127.00086</v>
-      </c>
-      <c r="M25" t="s">
-        <v>99</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>127.001</v>
+      </c>
+      <c r="L25" t="s">
+        <v>98</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F26">
         <v>81.667</v>
       </c>
       <c r="G26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I26" s="1">
-        <v>1.704</v>
+        <v>139.161</v>
       </c>
       <c r="J26">
-        <v>139.160568</v>
+        <v>1.74</v>
       </c>
       <c r="K26" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L26" s="1">
-        <v>142.10058</v>
-      </c>
-      <c r="M26" t="s">
-        <v>100</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>142.101</v>
+      </c>
+      <c r="L26" t="s">
+        <v>99</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F27">
         <v>39.76</v>
       </c>
       <c r="G27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27">
-        <v>1.716</v>
+        <v>1.796</v>
       </c>
       <c r="I27" s="1">
-        <v>1.796</v>
+        <v>71.40900000000001</v>
       </c>
       <c r="J27">
-        <v>71.40895999999999</v>
+        <v>2</v>
       </c>
       <c r="K27" s="1">
-        <v>2</v>
-      </c>
-      <c r="L27" s="1">
         <v>79.52</v>
       </c>
-      <c r="M27" t="s">
-        <v>101</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="L27" t="s">
+        <v>100</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="3" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2110,89 +2026,89 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:14">
       <c r="A31" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="E31" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="6">
         <v>1833.909</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="7">
         <v>21</v>
       </c>
       <c r="D32" s="7">
-        <v>1.544428</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2832.34</v>
-      </c>
-      <c r="F32" s="6">
-        <v>2979.77</v>
+        <v>1.544</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2832.344</v>
+      </c>
+      <c r="F32" s="7">
+        <v>2979.768</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="6">
         <v>161.544</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="7">
         <v>4</v>
       </c>
       <c r="D33" s="7">
-        <v>1.728672</v>
-      </c>
-      <c r="E33" s="6">
-        <v>279.26</v>
-      </c>
-      <c r="F33" s="6">
-        <v>310.38</v>
+        <v>1.729</v>
+      </c>
+      <c r="E33" s="7">
+        <v>279.256</v>
+      </c>
+      <c r="F33" s="7">
+        <v>310.379</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" s="6">
         <v>1</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="7">
         <v>1</v>
       </c>
       <c r="D34" s="7">
         <v>26.83</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="7">
         <v>26.83</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="7">
         <v>26.83</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="9">
         <v>1996.453</v>
@@ -2205,7 +2121,7 @@
         <v>3138.43</v>
       </c>
       <c r="F35" s="9">
-        <v>3316.98</v>
+        <v>3316.977</v>
       </c>
     </row>
   </sheetData>
